--- a/results/hammaddeKullanım.xlsx
+++ b/results/hammaddeKullanım.xlsx
@@ -1,29 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10511"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/begumyilmaz/Documents/okul/koç/4.2/bitirme/bitirmeRepoYeni/indr491/results/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACB3D9BE-7789-2149-BF48-08B5865AEDCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$82</definedName>
-  </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="108">
   <si>
     <t>Hammadde</t>
   </si>
@@ -298,7 +289,10 @@
     <t>%18.677004073865035</t>
   </si>
   <si>
-    <t>%73.18448657208447</t>
+    <t>%33.53949083072654</t>
+  </si>
+  <si>
+    <t>%9.158972153597285</t>
   </si>
   <si>
     <t>%30.861108337263666</t>
@@ -307,9 +301,6 @@
     <t>%25.994754289615006</t>
   </si>
   <si>
-    <t>%10.051454619804389</t>
-  </si>
-  <si>
     <t>%36.45794242723614</t>
   </si>
   <si>
@@ -325,7 +316,10 @@
     <t>%2.0552068633999783</t>
   </si>
   <si>
-    <t>%38.130564908611944</t>
+    <t>%19.065282454305972</t>
+  </si>
+  <si>
+    <t>%4.2085555306482965</t>
   </si>
   <si>
     <t>%33.36352768706696</t>
@@ -349,8 +343,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -413,21 +407,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -465,7 +451,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -499,7 +485,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -534,10 +519,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -710,18 +694,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E82"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.1640625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -738,7 +715,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>30004224</v>
       </c>
@@ -746,7 +723,7 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>0.40170268005059778</v>
+        <v>0.4017026800505978</v>
       </c>
       <c r="D2">
         <v>21.6</v>
@@ -755,7 +732,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>30005768</v>
       </c>
@@ -763,16 +740,16 @@
         <v>6</v>
       </c>
       <c r="C3">
-        <v>283.16000000000003</v>
+        <v>283.16</v>
       </c>
       <c r="D3">
-        <v>283.16000000000003</v>
+        <v>283.16</v>
       </c>
       <c r="E3" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>30005777</v>
       </c>
@@ -789,7 +766,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>30003732</v>
       </c>
@@ -797,7 +774,7 @@
         <v>8</v>
       </c>
       <c r="C5">
-        <v>33.297646948815441</v>
+        <v>33.29764694881544</v>
       </c>
       <c r="D5">
         <v>48.7</v>
@@ -806,7 +783,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>30005780</v>
       </c>
@@ -823,7 +800,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>30005788</v>
       </c>
@@ -840,7 +817,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>30005794</v>
       </c>
@@ -848,16 +825,16 @@
         <v>11</v>
       </c>
       <c r="C8">
-        <v>18.940000000000001</v>
+        <v>18.94</v>
       </c>
       <c r="D8">
-        <v>18.940000000000001</v>
+        <v>18.94</v>
       </c>
       <c r="E8" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>30004772</v>
       </c>
@@ -865,16 +842,16 @@
         <v>12</v>
       </c>
       <c r="C9">
-        <v>19.399999999999999</v>
+        <v>19.4</v>
       </c>
       <c r="D9">
-        <v>19.399999999999999</v>
+        <v>19.4</v>
       </c>
       <c r="E9" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>30005804</v>
       </c>
@@ -891,7 +868,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>30005805</v>
       </c>
@@ -908,7 +885,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>30005809</v>
       </c>
@@ -925,7 +902,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>30005812</v>
       </c>
@@ -942,7 +919,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>30005818</v>
       </c>
@@ -959,7 +936,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>30005820</v>
       </c>
@@ -976,7 +953,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>30003778</v>
       </c>
@@ -993,7 +970,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>30005834</v>
       </c>
@@ -1010,7 +987,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>30005841</v>
       </c>
@@ -1027,7 +1004,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>30005842</v>
       </c>
@@ -1035,7 +1012,7 @@
         <v>22</v>
       </c>
       <c r="C19">
-        <v>18.251168380980911</v>
+        <v>18.25116838098091</v>
       </c>
       <c r="D19">
         <v>97.72</v>
@@ -1044,7 +1021,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>30005845</v>
       </c>
@@ -1061,7 +1038,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>30005848</v>
       </c>
@@ -1069,16 +1046,16 @@
         <v>24</v>
       </c>
       <c r="C21">
-        <v>18.760000000000002</v>
+        <v>18.76</v>
       </c>
       <c r="D21">
-        <v>18.760000000000002</v>
+        <v>18.76</v>
       </c>
       <c r="E21" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>30005851</v>
       </c>
@@ -1086,16 +1063,16 @@
         <v>25</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>8.301023980604819</v>
       </c>
       <c r="D22">
         <v>24.75</v>
       </c>
       <c r="E22" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>30005855</v>
       </c>
@@ -1103,16 +1080,16 @@
         <v>26</v>
       </c>
       <c r="C23">
-        <v>30.715529014303851</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>41.97</v>
       </c>
       <c r="E23" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>30005856</v>
       </c>
@@ -1123,13 +1100,13 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>662.82</v>
+        <v>662.8200000000001</v>
       </c>
       <c r="E24" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>30005857</v>
       </c>
@@ -1137,16 +1114,16 @@
         <v>28</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>30.71552901430385</v>
       </c>
       <c r="D25">
         <v>335.36</v>
       </c>
       <c r="E25" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>30005858</v>
       </c>
@@ -1157,13 +1134,13 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>314.77999999999997</v>
+        <v>314.78</v>
       </c>
       <c r="E26" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>30005859</v>
       </c>
@@ -1177,10 +1154,10 @@
         <v>122.44</v>
       </c>
       <c r="E27" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>30005861</v>
       </c>
@@ -1197,7 +1174,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>30005862</v>
       </c>
@@ -1205,16 +1182,16 @@
         <v>32</v>
       </c>
       <c r="C29">
-        <v>25.363081760377359</v>
+        <v>25.36308176037736</v>
       </c>
       <c r="D29">
-        <v>97.57</v>
+        <v>97.56999999999999</v>
       </c>
       <c r="E29" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30">
         <v>30005864</v>
       </c>
@@ -1231,7 +1208,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5">
       <c r="A31">
         <v>30005865</v>
       </c>
@@ -1248,7 +1225,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5">
       <c r="A32">
         <v>30005866</v>
       </c>
@@ -1265,7 +1242,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5">
       <c r="A33">
         <v>30005867</v>
       </c>
@@ -1282,7 +1259,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5">
       <c r="A34">
         <v>30005868</v>
       </c>
@@ -1299,7 +1276,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5">
       <c r="A35">
         <v>30005869</v>
       </c>
@@ -1316,7 +1293,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5">
       <c r="A36">
         <v>30005870</v>
       </c>
@@ -1333,7 +1310,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5">
       <c r="A37">
         <v>30005872</v>
       </c>
@@ -1341,16 +1318,16 @@
         <v>40</v>
       </c>
       <c r="C37">
-        <v>27.48</v>
+        <v>0</v>
       </c>
       <c r="D37">
         <v>27.48</v>
       </c>
       <c r="E37" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38">
         <v>30005873</v>
       </c>
@@ -1358,16 +1335,16 @@
         <v>41</v>
       </c>
       <c r="C38">
-        <v>2.7490728385165011</v>
+        <v>27.35</v>
       </c>
       <c r="D38">
         <v>27.35</v>
       </c>
       <c r="E38" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39">
         <v>30005876</v>
       </c>
@@ -1384,7 +1361,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5">
       <c r="A40">
         <v>30005886</v>
       </c>
@@ -1401,7 +1378,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5">
       <c r="A41">
         <v>30003956</v>
       </c>
@@ -1409,7 +1386,7 @@
         <v>44</v>
       </c>
       <c r="C41">
-        <v>7.7363753830595083</v>
+        <v>7.736375383059508</v>
       </c>
       <c r="D41">
         <v>21.22</v>
@@ -1418,7 +1395,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5">
       <c r="A42">
         <v>30005037</v>
       </c>
@@ -1435,7 +1412,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5">
       <c r="A43">
         <v>30001483</v>
       </c>
@@ -1443,16 +1420,16 @@
         <v>46</v>
       </c>
       <c r="C43">
-        <v>1.5607082513080299</v>
+        <v>1.56070825130803</v>
       </c>
       <c r="D43">
-        <v>40.159999999999997</v>
+        <v>40.16</v>
       </c>
       <c r="E43" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5">
       <c r="A44">
         <v>30003535</v>
       </c>
@@ -1460,16 +1437,16 @@
         <v>47</v>
       </c>
       <c r="C44">
-        <v>149.30000000000001</v>
+        <v>149.3</v>
       </c>
       <c r="D44">
-        <v>149.30000000000001</v>
+        <v>149.3</v>
       </c>
       <c r="E44" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5">
       <c r="A45">
         <v>30003536</v>
       </c>
@@ -1486,7 +1463,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5">
       <c r="A46">
         <v>30003537</v>
       </c>
@@ -1503,7 +1480,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5">
       <c r="A47">
         <v>30003543</v>
       </c>
@@ -1520,7 +1497,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5">
       <c r="A48">
         <v>30003546</v>
       </c>
@@ -1528,16 +1505,16 @@
         <v>51</v>
       </c>
       <c r="C48">
-        <v>70.930000000000007</v>
+        <v>70.93000000000001</v>
       </c>
       <c r="D48">
-        <v>70.930000000000007</v>
+        <v>70.93000000000001</v>
       </c>
       <c r="E48" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5">
       <c r="A49">
         <v>30003547</v>
       </c>
@@ -1545,16 +1522,16 @@
         <v>52</v>
       </c>
       <c r="C49">
-        <v>92.76</v>
+        <v>92.76000000000001</v>
       </c>
       <c r="D49">
-        <v>92.76</v>
+        <v>92.76000000000001</v>
       </c>
       <c r="E49" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5">
       <c r="A50">
         <v>30003550</v>
       </c>
@@ -1562,7 +1539,7 @@
         <v>53</v>
       </c>
       <c r="C50">
-        <v>761.23000000000013</v>
+        <v>761.2300000000001</v>
       </c>
       <c r="D50">
         <v>761.23</v>
@@ -1571,7 +1548,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5">
       <c r="A51">
         <v>30003551</v>
       </c>
@@ -1588,7 +1565,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5">
       <c r="A52">
         <v>30003555</v>
       </c>
@@ -1605,7 +1582,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5">
       <c r="A53">
         <v>30003563</v>
       </c>
@@ -1613,16 +1590,16 @@
         <v>56</v>
       </c>
       <c r="C53">
-        <v>134.52000000000001</v>
+        <v>134.52</v>
       </c>
       <c r="D53">
-        <v>134.52000000000001</v>
+        <v>134.52</v>
       </c>
       <c r="E53" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5">
       <c r="A54">
         <v>30004110</v>
       </c>
@@ -1630,7 +1607,7 @@
         <v>57</v>
       </c>
       <c r="C54">
-        <v>0.54154700850589432</v>
+        <v>0.5415470085058943</v>
       </c>
       <c r="D54">
         <v>26.35</v>
@@ -1639,7 +1616,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5">
       <c r="A55">
         <v>30005704</v>
       </c>
@@ -1647,16 +1624,16 @@
         <v>58</v>
       </c>
       <c r="C55">
-        <v>134.58000000000001</v>
+        <v>134.58</v>
       </c>
       <c r="D55">
-        <v>134.58000000000001</v>
+        <v>134.58</v>
       </c>
       <c r="E55" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5">
       <c r="A56">
         <v>30005707</v>
       </c>
@@ -1673,7 +1650,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5">
       <c r="A57">
         <v>30003660</v>
       </c>
@@ -1681,16 +1658,16 @@
         <v>60</v>
       </c>
       <c r="C57">
-        <v>626.41999999999996</v>
+        <v>626.42</v>
       </c>
       <c r="D57">
-        <v>626.41999999999996</v>
+        <v>626.42</v>
       </c>
       <c r="E57" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5">
       <c r="A58">
         <v>30005708</v>
       </c>
@@ -1707,7 +1684,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5">
       <c r="A59">
         <v>30003662</v>
       </c>
@@ -1715,16 +1692,16 @@
         <v>62</v>
       </c>
       <c r="C59">
-        <v>635.63999999999987</v>
+        <v>635.64</v>
       </c>
       <c r="D59">
         <v>635.64</v>
       </c>
       <c r="E59" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
       <c r="A60">
         <v>30005710</v>
       </c>
@@ -1732,16 +1709,16 @@
         <v>63</v>
       </c>
       <c r="C60">
-        <v>17.760000000000002</v>
+        <v>17.76</v>
       </c>
       <c r="D60">
-        <v>17.760000000000002</v>
+        <v>17.76</v>
       </c>
       <c r="E60" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5">
       <c r="A61">
         <v>30005712</v>
       </c>
@@ -1758,7 +1735,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5">
       <c r="A62">
         <v>30003665</v>
       </c>
@@ -1775,7 +1752,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5">
       <c r="A63">
         <v>30003666</v>
       </c>
@@ -1792,7 +1769,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5">
       <c r="A64">
         <v>30005711</v>
       </c>
@@ -1800,16 +1777,16 @@
         <v>67</v>
       </c>
       <c r="C64">
-        <v>34.299999999999997</v>
+        <v>34.3</v>
       </c>
       <c r="D64">
-        <v>34.299999999999997</v>
+        <v>34.3</v>
       </c>
       <c r="E64" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5">
       <c r="A65">
         <v>30003669</v>
       </c>
@@ -1826,7 +1803,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5">
       <c r="A66">
         <v>30005718</v>
       </c>
@@ -1834,7 +1811,7 @@
         <v>69</v>
       </c>
       <c r="C66">
-        <v>16.602047961209639</v>
+        <v>8.301023980604819</v>
       </c>
       <c r="D66">
         <v>43.54</v>
@@ -1843,7 +1820,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5">
       <c r="A67">
         <v>30003671</v>
       </c>
@@ -1851,16 +1828,16 @@
         <v>70</v>
       </c>
       <c r="C67">
-        <v>314.70999999999998</v>
+        <v>314.71</v>
       </c>
       <c r="D67">
-        <v>314.70999999999998</v>
+        <v>314.71</v>
       </c>
       <c r="E67" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
       <c r="A68">
         <v>30005724</v>
       </c>
@@ -1877,7 +1854,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5">
       <c r="A69">
         <v>30005727</v>
       </c>
@@ -1894,7 +1871,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5">
       <c r="A70">
         <v>30005729</v>
       </c>
@@ -1902,16 +1879,16 @@
         <v>73</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>2.8790728385165</v>
       </c>
       <c r="D70">
         <v>68.41</v>
       </c>
       <c r="E70" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
       <c r="A71">
         <v>30005730</v>
       </c>
@@ -1919,16 +1896,16 @@
         <v>74</v>
       </c>
       <c r="C71">
-        <v>269.95431157436491</v>
+        <v>269.9543115743649</v>
       </c>
       <c r="D71">
         <v>809.13</v>
       </c>
       <c r="E71" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
       <c r="A72">
         <v>30005735</v>
       </c>
@@ -1936,16 +1913,16 @@
         <v>75</v>
       </c>
       <c r="C72">
-        <v>26.891328185209129</v>
+        <v>26.89132818520913</v>
       </c>
       <c r="D72">
         <v>150.12</v>
       </c>
       <c r="E72" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
       <c r="A73">
         <v>30005736</v>
       </c>
@@ -1953,16 +1930,16 @@
         <v>76</v>
       </c>
       <c r="C73">
-        <v>8.7664311231697862</v>
+        <v>8.766431123169786</v>
       </c>
       <c r="D73">
         <v>21.68</v>
       </c>
       <c r="E73" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
       <c r="A74">
         <v>30005737</v>
       </c>
@@ -1979,7 +1956,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5">
       <c r="A75">
         <v>30003694</v>
       </c>
@@ -1996,7 +1973,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5">
       <c r="A76">
         <v>30003695</v>
       </c>
@@ -2004,16 +1981,16 @@
         <v>79</v>
       </c>
       <c r="C76">
-        <v>75.180000000000007</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="D76">
-        <v>75.180000000000007</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="E76" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5">
       <c r="A77">
         <v>30003696</v>
       </c>
@@ -2021,16 +1998,16 @@
         <v>80</v>
       </c>
       <c r="C77">
-        <v>75.040000000000006</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="D77">
-        <v>75.040000000000006</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="E77" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5">
       <c r="A78">
         <v>30005745</v>
       </c>
@@ -2038,16 +2015,16 @@
         <v>81</v>
       </c>
       <c r="C78">
-        <v>36.766453060826628</v>
+        <v>36.76645306082663</v>
       </c>
       <c r="D78">
         <v>38.86</v>
       </c>
       <c r="E78" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
       <c r="A79">
         <v>30003698</v>
       </c>
@@ -2064,7 +2041,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5">
       <c r="A80">
         <v>30005755</v>
       </c>
@@ -2072,16 +2049,16 @@
         <v>83</v>
       </c>
       <c r="C80">
-        <v>22.671804628887379</v>
+        <v>22.67180462888738</v>
       </c>
       <c r="D80">
         <v>36.06</v>
       </c>
       <c r="E80" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
       <c r="A81">
         <v>30005757</v>
       </c>
@@ -2098,7 +2075,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:5">
       <c r="A82">
         <v>30004223</v>
       </c>
@@ -2106,17 +2083,16 @@
         <v>85</v>
       </c>
       <c r="C82">
-        <v>0.24353255793601691</v>
+        <v>0.2435325579360169</v>
       </c>
       <c r="D82">
         <v>21.08</v>
       </c>
       <c r="E82" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E82" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>